--- a/data/processed/positivacao/2023-08_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2023-08_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -25179,7 +25179,7 @@
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B956" t="inlineStr"/>
@@ -36687,7 +36687,7 @@
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1399" t="inlineStr"/>
@@ -65631,7 +65631,7 @@
     <row r="2513">
       <c r="A2513" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2513" t="inlineStr"/>
@@ -67354,12 +67354,12 @@
       <c r="A2580" t="inlineStr"/>
       <c r="B2580" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 8 cliente(s), não positivou 87 cliente(s) - Total vendido: R$ 11.807,65
+          <t>Vendedor 1 - VENDEDOR 01: positivou 8 cliente(s), não positivou 87 cliente(s) - Total vendido: R$ 11.807,65
 Vendedor 18 - LOJA: positivou 126 cliente(s), não positivou 725 cliente(s) - Total vendido: R$ 74.666,14
-Vendedor 3 - FERNANDA: positivou 103 cliente(s), não positivou 339 cliente(s) - Total vendido: R$ 166.261,91
-Vendedor 4 - DANIELA: positivou 85 cliente(s), não positivou 579 cliente(s) - Total vendido: R$ 48.362,46
+Vendedor 3 - VENDEDOR 03: positivou 103 cliente(s), não positivou 339 cliente(s) - Total vendido: R$ 166.261,91
+Vendedor 4 - VENDEDOR 04: positivou 85 cliente(s), não positivou 579 cliente(s) - Total vendido: R$ 48.362,46
 Vendedor 5 - SITE: positivou 5 cliente(s), não positivou 443 cliente(s) - Total vendido: R$ 595,13
-Vendedor 8 - RAFAEL: positivou 4 cliente(s), não positivou 61 cliente(s) - Total vendido: R$ 1.663,14</t>
+Vendedor 8 - VENDEDOR 08: positivou 4 cliente(s), não positivou 61 cliente(s) - Total vendido: R$ 1.663,14</t>
         </is>
       </c>
       <c r="C2580" t="inlineStr"/>
